--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QC\Downloads\namdogeum-dashboard-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QC\Downloads\namdogeum-dashboard-main (1)\namdogeum-dashboard-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7193BC27-2947-4A88-81AC-B5247D4BD4B7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04D4BEB-3300-49FB-9E7D-BDD491C7F8AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FBDE3CB-3BE6-4858-BD36-C283BF315A42}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$B$3:$P$162</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateCount="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="230">
   <si>
     <t>사출 불량 유형</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -831,6 +831,18 @@
   </si>
   <si>
     <t>RU #6932-1 RU 2nd Row Chrome handle RH LH Body</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PNL-FACIA, LH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NQ5 NOZZLE ASSY DEFROSTER NO.2,LH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRKT-RR CORNER RADAR MTG,RH   866G2-BS010</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1081,7 +1093,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1227,6 +1239,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -21191,7 +21206,7 @@
         <v>150</v>
       </c>
       <c r="E657" s="43">
-        <f t="shared" ref="E657:E659" si="20">D657-F657</f>
+        <f t="shared" ref="E657:E683" si="20">D657-F657</f>
         <v>150</v>
       </c>
       <c r="F657" s="8">
@@ -21272,6 +21287,740 @@
       <c r="N659" s="26"/>
       <c r="O659" s="26"/>
       <c r="P659" s="26"/>
+    </row>
+    <row r="660" spans="2:16">
+      <c r="B660" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C660" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="D660" s="26">
+        <v>128</v>
+      </c>
+      <c r="E660" s="43">
+        <f t="shared" si="20"/>
+        <v>120</v>
+      </c>
+      <c r="F660" s="8">
+        <f t="shared" ref="F660:F683" si="21">SUM(G660:P660)</f>
+        <v>8</v>
+      </c>
+      <c r="G660" s="26">
+        <v>4</v>
+      </c>
+      <c r="H660" s="26">
+        <v>4</v>
+      </c>
+      <c r="I660" s="33"/>
+      <c r="J660" s="33"/>
+      <c r="K660" s="33"/>
+      <c r="L660" s="26"/>
+      <c r="M660" s="26"/>
+      <c r="N660" s="26"/>
+      <c r="O660" s="26"/>
+      <c r="P660" s="33"/>
+    </row>
+    <row r="661" spans="2:16">
+      <c r="B661" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C661" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D661" s="26">
+        <v>399</v>
+      </c>
+      <c r="E661" s="43">
+        <f t="shared" si="20"/>
+        <v>390</v>
+      </c>
+      <c r="F661" s="8">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="G661" s="26"/>
+      <c r="H661" s="26">
+        <v>9</v>
+      </c>
+      <c r="I661" s="26"/>
+      <c r="J661" s="26"/>
+      <c r="K661" s="26"/>
+      <c r="L661" s="26"/>
+      <c r="M661" s="26"/>
+      <c r="N661" s="26"/>
+      <c r="O661" s="26"/>
+      <c r="P661" s="26"/>
+    </row>
+    <row r="662" spans="2:16">
+      <c r="B662" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C662" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D662" s="26">
+        <v>1082</v>
+      </c>
+      <c r="E662" s="43">
+        <f t="shared" si="20"/>
+        <v>1080</v>
+      </c>
+      <c r="F662" s="8">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+      <c r="G662" s="26"/>
+      <c r="H662" s="26">
+        <v>2</v>
+      </c>
+      <c r="I662" s="26"/>
+      <c r="J662" s="26"/>
+      <c r="K662" s="26"/>
+      <c r="L662" s="26"/>
+      <c r="M662" s="26"/>
+      <c r="N662" s="26"/>
+      <c r="O662" s="26"/>
+      <c r="P662" s="26"/>
+    </row>
+    <row r="663" spans="2:16">
+      <c r="B663" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C663" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="D663" s="26">
+        <v>10</v>
+      </c>
+      <c r="E663" s="43">
+        <f t="shared" si="20"/>
+        <v>10</v>
+      </c>
+      <c r="F663" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G663" s="26"/>
+      <c r="H663" s="26"/>
+      <c r="I663" s="26"/>
+      <c r="J663" s="26"/>
+      <c r="K663" s="26"/>
+      <c r="L663" s="26"/>
+      <c r="M663" s="26"/>
+      <c r="N663" s="26"/>
+      <c r="O663" s="26"/>
+      <c r="P663" s="26"/>
+    </row>
+    <row r="664" spans="2:16">
+      <c r="B664" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C664" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="D664" s="26">
+        <v>309</v>
+      </c>
+      <c r="E664" s="43">
+        <f t="shared" si="20"/>
+        <v>300</v>
+      </c>
+      <c r="F664" s="8">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="G664" s="26">
+        <v>4</v>
+      </c>
+      <c r="H664" s="26">
+        <v>5</v>
+      </c>
+      <c r="I664" s="26"/>
+      <c r="J664" s="26"/>
+      <c r="K664" s="26"/>
+      <c r="L664" s="26"/>
+      <c r="M664" s="26"/>
+      <c r="N664" s="26"/>
+      <c r="O664" s="26"/>
+      <c r="P664" s="26"/>
+    </row>
+    <row r="665" spans="2:16">
+      <c r="B665" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C665" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D665" s="26">
+        <v>40</v>
+      </c>
+      <c r="E665" s="43">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="F665" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G665" s="26"/>
+      <c r="H665" s="26"/>
+      <c r="I665" s="26"/>
+      <c r="J665" s="26"/>
+      <c r="K665" s="26"/>
+      <c r="L665" s="26"/>
+      <c r="M665" s="26"/>
+      <c r="N665" s="26"/>
+      <c r="O665" s="26"/>
+      <c r="P665" s="26"/>
+    </row>
+    <row r="666" spans="2:16">
+      <c r="B666" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C666" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="D666" s="26">
+        <v>320</v>
+      </c>
+      <c r="E666" s="43">
+        <f t="shared" si="20"/>
+        <v>320</v>
+      </c>
+      <c r="F666" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G666" s="26"/>
+      <c r="H666" s="26"/>
+      <c r="I666" s="26"/>
+      <c r="J666" s="26"/>
+      <c r="K666" s="26"/>
+      <c r="L666" s="26"/>
+      <c r="M666" s="26"/>
+      <c r="N666" s="26"/>
+      <c r="O666" s="26"/>
+      <c r="P666" s="26"/>
+    </row>
+    <row r="667" spans="2:16">
+      <c r="B667" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C667" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="D667" s="26">
+        <v>1017</v>
+      </c>
+      <c r="E667" s="43">
+        <f t="shared" si="20"/>
+        <v>995</v>
+      </c>
+      <c r="F667" s="8">
+        <f t="shared" si="21"/>
+        <v>22</v>
+      </c>
+      <c r="G667" s="26"/>
+      <c r="H667" s="26">
+        <v>22</v>
+      </c>
+      <c r="I667" s="26"/>
+      <c r="J667" s="26"/>
+      <c r="K667" s="26"/>
+      <c r="L667" s="26"/>
+      <c r="M667" s="26"/>
+      <c r="N667" s="26"/>
+      <c r="O667" s="26"/>
+      <c r="P667" s="26"/>
+    </row>
+    <row r="668" spans="2:16">
+      <c r="B668" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C668" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D668" s="26">
+        <v>1818</v>
+      </c>
+      <c r="E668" s="43">
+        <f t="shared" si="20"/>
+        <v>1800</v>
+      </c>
+      <c r="F668" s="8">
+        <f t="shared" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="G668" s="26"/>
+      <c r="H668" s="26">
+        <v>18</v>
+      </c>
+      <c r="I668" s="26"/>
+      <c r="J668" s="26"/>
+      <c r="K668" s="26"/>
+      <c r="L668" s="26"/>
+      <c r="M668" s="26"/>
+      <c r="N668" s="26"/>
+      <c r="O668" s="26"/>
+      <c r="P668" s="26"/>
+    </row>
+    <row r="669" spans="2:16">
+      <c r="B669" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C669" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D669" s="26">
+        <v>149</v>
+      </c>
+      <c r="E669" s="43">
+        <f t="shared" si="20"/>
+        <v>135</v>
+      </c>
+      <c r="F669" s="8">
+        <f t="shared" si="21"/>
+        <v>14</v>
+      </c>
+      <c r="G669" s="26">
+        <v>14</v>
+      </c>
+      <c r="H669" s="26"/>
+      <c r="I669" s="26"/>
+      <c r="J669" s="26"/>
+      <c r="K669" s="26"/>
+      <c r="L669" s="26"/>
+      <c r="M669" s="26"/>
+      <c r="N669" s="26"/>
+      <c r="O669" s="26"/>
+      <c r="P669" s="26"/>
+    </row>
+    <row r="670" spans="2:16">
+      <c r="B670" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C670" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D670" s="26">
+        <v>150</v>
+      </c>
+      <c r="E670" s="43">
+        <f t="shared" si="20"/>
+        <v>140</v>
+      </c>
+      <c r="F670" s="8">
+        <f t="shared" si="21"/>
+        <v>10</v>
+      </c>
+      <c r="G670" s="26">
+        <v>3</v>
+      </c>
+      <c r="H670" s="26">
+        <v>7</v>
+      </c>
+      <c r="I670" s="26"/>
+      <c r="J670" s="26"/>
+      <c r="K670" s="26"/>
+      <c r="L670" s="26"/>
+      <c r="M670" s="26"/>
+      <c r="N670" s="26"/>
+      <c r="O670" s="26"/>
+      <c r="P670" s="26"/>
+    </row>
+    <row r="671" spans="2:16">
+      <c r="B671" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C671" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D671" s="26">
+        <v>150</v>
+      </c>
+      <c r="E671" s="43">
+        <f t="shared" si="20"/>
+        <v>140</v>
+      </c>
+      <c r="F671" s="8">
+        <f t="shared" si="21"/>
+        <v>10</v>
+      </c>
+      <c r="G671" s="26">
+        <v>3</v>
+      </c>
+      <c r="H671" s="26">
+        <v>7</v>
+      </c>
+      <c r="I671" s="26"/>
+      <c r="J671" s="26"/>
+      <c r="K671" s="26"/>
+      <c r="L671" s="26"/>
+      <c r="M671" s="26"/>
+      <c r="N671" s="26"/>
+      <c r="O671" s="26"/>
+      <c r="P671" s="26"/>
+    </row>
+    <row r="672" spans="2:16">
+      <c r="B672" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C672" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D672" s="26">
+        <v>1700</v>
+      </c>
+      <c r="E672" s="43">
+        <f t="shared" si="20"/>
+        <v>1700</v>
+      </c>
+      <c r="F672" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G672" s="26"/>
+      <c r="H672" s="26"/>
+      <c r="I672" s="26"/>
+      <c r="J672" s="26"/>
+      <c r="K672" s="26"/>
+      <c r="L672" s="26"/>
+      <c r="M672" s="26"/>
+      <c r="N672" s="26"/>
+      <c r="O672" s="26"/>
+      <c r="P672" s="26"/>
+    </row>
+    <row r="673" spans="2:16">
+      <c r="B673" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C673" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="D673" s="26">
+        <v>590</v>
+      </c>
+      <c r="E673" s="43">
+        <f t="shared" si="20"/>
+        <v>590</v>
+      </c>
+      <c r="F673" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G673" s="26"/>
+      <c r="H673" s="26"/>
+      <c r="I673" s="26"/>
+      <c r="J673" s="26"/>
+      <c r="K673" s="26"/>
+      <c r="L673" s="26"/>
+      <c r="M673" s="26"/>
+      <c r="N673" s="26"/>
+      <c r="O673" s="26"/>
+      <c r="P673" s="26"/>
+    </row>
+    <row r="674" spans="2:16">
+      <c r="B674" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C674" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="D674" s="26">
+        <v>1161</v>
+      </c>
+      <c r="E674" s="43">
+        <f t="shared" si="20"/>
+        <v>1152</v>
+      </c>
+      <c r="F674" s="8">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="G674" s="26"/>
+      <c r="H674" s="26"/>
+      <c r="I674" s="26"/>
+      <c r="J674" s="26">
+        <v>9</v>
+      </c>
+      <c r="K674" s="26"/>
+      <c r="L674" s="26"/>
+      <c r="M674" s="26"/>
+      <c r="N674" s="26"/>
+      <c r="O674" s="26"/>
+      <c r="P674" s="26"/>
+    </row>
+    <row r="675" spans="2:16">
+      <c r="B675" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C675" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D675" s="26">
+        <v>2290</v>
+      </c>
+      <c r="E675" s="43">
+        <f t="shared" si="20"/>
+        <v>2290</v>
+      </c>
+      <c r="F675" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G675" s="26"/>
+      <c r="H675" s="26"/>
+      <c r="I675" s="26"/>
+      <c r="J675" s="26"/>
+      <c r="K675" s="26"/>
+      <c r="L675" s="26"/>
+      <c r="M675" s="26"/>
+      <c r="N675" s="26"/>
+      <c r="O675" s="26"/>
+      <c r="P675" s="26"/>
+    </row>
+    <row r="676" spans="2:16">
+      <c r="B676" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C676" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D676" s="26">
+        <v>1120</v>
+      </c>
+      <c r="E676" s="43">
+        <f t="shared" si="20"/>
+        <v>1120</v>
+      </c>
+      <c r="F676" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G676" s="26"/>
+      <c r="H676" s="26"/>
+      <c r="I676" s="26"/>
+      <c r="J676" s="26"/>
+      <c r="K676" s="26"/>
+      <c r="L676" s="26"/>
+      <c r="M676" s="26"/>
+      <c r="N676" s="26"/>
+      <c r="O676" s="26"/>
+      <c r="P676" s="26"/>
+    </row>
+    <row r="677" spans="2:16">
+      <c r="B677" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C677" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="D677" s="26">
+        <v>300</v>
+      </c>
+      <c r="E677" s="43">
+        <f t="shared" si="20"/>
+        <v>300</v>
+      </c>
+      <c r="F677" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G677" s="26"/>
+      <c r="H677" s="26"/>
+      <c r="I677" s="26"/>
+      <c r="J677" s="26"/>
+      <c r="K677" s="26"/>
+      <c r="L677" s="26"/>
+      <c r="M677" s="26"/>
+      <c r="N677" s="26"/>
+      <c r="O677" s="26"/>
+      <c r="P677" s="26"/>
+    </row>
+    <row r="678" spans="2:16">
+      <c r="B678" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C678" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D678" s="26">
+        <v>330</v>
+      </c>
+      <c r="E678" s="43">
+        <f t="shared" si="20"/>
+        <v>330</v>
+      </c>
+      <c r="F678" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G678" s="26"/>
+      <c r="H678" s="26"/>
+      <c r="I678" s="26"/>
+      <c r="J678" s="26"/>
+      <c r="K678" s="26"/>
+      <c r="L678" s="26"/>
+      <c r="M678" s="26"/>
+      <c r="N678" s="26"/>
+      <c r="O678" s="26"/>
+      <c r="P678" s="26"/>
+    </row>
+    <row r="679" spans="2:16">
+      <c r="B679" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C679" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="D679" s="26">
+        <v>5</v>
+      </c>
+      <c r="E679" s="43">
+        <f t="shared" si="20"/>
+        <v>5</v>
+      </c>
+      <c r="F679" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G679" s="26"/>
+      <c r="H679" s="26"/>
+      <c r="I679" s="26"/>
+      <c r="J679" s="26"/>
+      <c r="K679" s="26"/>
+      <c r="L679" s="26"/>
+      <c r="M679" s="26"/>
+      <c r="N679" s="26"/>
+      <c r="O679" s="26"/>
+      <c r="P679" s="26"/>
+    </row>
+    <row r="680" spans="2:16">
+      <c r="B680" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C680" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="D680" s="26">
+        <v>874</v>
+      </c>
+      <c r="E680" s="43">
+        <f t="shared" si="20"/>
+        <v>860</v>
+      </c>
+      <c r="F680" s="8">
+        <f t="shared" si="21"/>
+        <v>14</v>
+      </c>
+      <c r="G680" s="26"/>
+      <c r="H680" s="26">
+        <v>14</v>
+      </c>
+      <c r="I680" s="26"/>
+      <c r="J680" s="26"/>
+      <c r="K680" s="26"/>
+      <c r="L680" s="26"/>
+      <c r="M680" s="26"/>
+      <c r="N680" s="26"/>
+      <c r="O680" s="26"/>
+      <c r="P680" s="26"/>
+    </row>
+    <row r="681" spans="2:16">
+      <c r="B681" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C681" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D681" s="26">
+        <v>276</v>
+      </c>
+      <c r="E681" s="43">
+        <f t="shared" si="20"/>
+        <v>270</v>
+      </c>
+      <c r="F681" s="8">
+        <f t="shared" si="21"/>
+        <v>6</v>
+      </c>
+      <c r="G681" s="26"/>
+      <c r="H681" s="26"/>
+      <c r="I681" s="26"/>
+      <c r="J681" s="26"/>
+      <c r="K681" s="26"/>
+      <c r="L681" s="26"/>
+      <c r="M681" s="26"/>
+      <c r="N681" s="26"/>
+      <c r="O681" s="26"/>
+      <c r="P681" s="26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="682" spans="2:16">
+      <c r="B682" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C682" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D682" s="26">
+        <v>1148</v>
+      </c>
+      <c r="E682" s="43">
+        <f t="shared" si="20"/>
+        <v>1130</v>
+      </c>
+      <c r="F682" s="8">
+        <f t="shared" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="G682" s="26"/>
+      <c r="H682" s="26">
+        <v>3</v>
+      </c>
+      <c r="I682" s="26"/>
+      <c r="J682" s="26">
+        <v>10</v>
+      </c>
+      <c r="K682" s="26"/>
+      <c r="L682" s="26"/>
+      <c r="M682" s="26"/>
+      <c r="N682" s="26"/>
+      <c r="O682" s="26"/>
+      <c r="P682" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="683" spans="2:16">
+      <c r="B683" s="49">
+        <v>46091</v>
+      </c>
+      <c r="C683" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="D683" s="26">
+        <v>1400</v>
+      </c>
+      <c r="E683" s="43">
+        <f t="shared" si="20"/>
+        <v>1400</v>
+      </c>
+      <c r="F683" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G683" s="26"/>
+      <c r="H683" s="26"/>
+      <c r="I683" s="26"/>
+      <c r="J683" s="26"/>
+      <c r="K683" s="26"/>
+      <c r="L683" s="26"/>
+      <c r="M683" s="26"/>
+      <c r="N683" s="26"/>
+      <c r="O683" s="26"/>
+      <c r="P683" s="26"/>
     </row>
     <row r="63289" spans="2:2">
       <c r="B63289" s="15"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QC\Downloads\namdogeum-dashboard-main (1)\namdogeum-dashboard-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04D4BEB-3300-49FB-9E7D-BDD491C7F8AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784A0498-E2B5-40CD-BCB8-C12025129398}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FBDE3CB-3BE6-4858-BD36-C283BF315A42}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="238">
   <si>
     <t>사출 불량 유형</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -844,6 +844,34 @@
   <si>
     <t>BRKT-RR CORNER RADAR MTG,RH   866G2-BS010</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SAFETY GLASS DOOR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NQ5PE COVER HUD BLANKING</t>
+  </si>
+  <si>
+    <t>QZ TRIM ASSY-SIDE LID,LH </t>
+  </si>
+  <si>
+    <t>QZ TRIM ASSY-SIDE LID,RH </t>
+  </si>
+  <si>
+    <t>NQ5PE COVER HEAD UP DISPLAY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#6988 TRACER DVR IB LHD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOLDING ASSY-FR BPR L/PLATE [SHORT]   86519-BS010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MODLING ASSY-FR BPR L/PLATE [SHORT]   86519-BS110</t>
   </si>
 </sst>
 </file>
@@ -1235,13 +1263,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1594,25 +1622,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="31.5" customHeight="1">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
     </row>
     <row r="3" spans="2:16" s="1" customFormat="1">
       <c r="B3" s="13" t="s">
@@ -21206,7 +21234,7 @@
         <v>150</v>
       </c>
       <c r="E657" s="43">
-        <f t="shared" ref="E657:E683" si="20">D657-F657</f>
+        <f t="shared" ref="E657:E720" si="20">D657-F657</f>
         <v>150</v>
       </c>
       <c r="F657" s="8">
@@ -21289,7 +21317,7 @@
       <c r="P659" s="26"/>
     </row>
     <row r="660" spans="2:16">
-      <c r="B660" s="49">
+      <c r="B660" s="47">
         <v>46091</v>
       </c>
       <c r="C660" s="32" t="s">
@@ -21303,7 +21331,7 @@
         <v>120</v>
       </c>
       <c r="F660" s="8">
-        <f t="shared" ref="F660:F683" si="21">SUM(G660:P660)</f>
+        <f t="shared" ref="F660:F723" si="21">SUM(G660:P660)</f>
         <v>8</v>
       </c>
       <c r="G660" s="26">
@@ -21322,7 +21350,7 @@
       <c r="P660" s="33"/>
     </row>
     <row r="661" spans="2:16">
-      <c r="B661" s="49">
+      <c r="B661" s="47">
         <v>46091</v>
       </c>
       <c r="C661" s="31" t="s">
@@ -21353,7 +21381,7 @@
       <c r="P661" s="26"/>
     </row>
     <row r="662" spans="2:16">
-      <c r="B662" s="49">
+      <c r="B662" s="47">
         <v>46091</v>
       </c>
       <c r="C662" s="31" t="s">
@@ -21384,7 +21412,7 @@
       <c r="P662" s="26"/>
     </row>
     <row r="663" spans="2:16">
-      <c r="B663" s="49">
+      <c r="B663" s="47">
         <v>46091</v>
       </c>
       <c r="C663" s="31" t="s">
@@ -21413,7 +21441,7 @@
       <c r="P663" s="26"/>
     </row>
     <row r="664" spans="2:16">
-      <c r="B664" s="49">
+      <c r="B664" s="47">
         <v>46091</v>
       </c>
       <c r="C664" s="31" t="s">
@@ -21446,7 +21474,7 @@
       <c r="P664" s="26"/>
     </row>
     <row r="665" spans="2:16">
-      <c r="B665" s="49">
+      <c r="B665" s="47">
         <v>46091</v>
       </c>
       <c r="C665" s="32" t="s">
@@ -21475,7 +21503,7 @@
       <c r="P665" s="26"/>
     </row>
     <row r="666" spans="2:16">
-      <c r="B666" s="49">
+      <c r="B666" s="47">
         <v>46091</v>
       </c>
       <c r="C666" s="32" t="s">
@@ -21504,7 +21532,7 @@
       <c r="P666" s="26"/>
     </row>
     <row r="667" spans="2:16">
-      <c r="B667" s="49">
+      <c r="B667" s="47">
         <v>46091</v>
       </c>
       <c r="C667" s="31" t="s">
@@ -21535,7 +21563,7 @@
       <c r="P667" s="26"/>
     </row>
     <row r="668" spans="2:16">
-      <c r="B668" s="49">
+      <c r="B668" s="47">
         <v>46091</v>
       </c>
       <c r="C668" s="32" t="s">
@@ -21566,7 +21594,7 @@
       <c r="P668" s="26"/>
     </row>
     <row r="669" spans="2:16">
-      <c r="B669" s="49">
+      <c r="B669" s="47">
         <v>46091</v>
       </c>
       <c r="C669" s="32" t="s">
@@ -21597,7 +21625,7 @@
       <c r="P669" s="26"/>
     </row>
     <row r="670" spans="2:16">
-      <c r="B670" s="49">
+      <c r="B670" s="47">
         <v>46091</v>
       </c>
       <c r="C670" s="32" t="s">
@@ -21630,7 +21658,7 @@
       <c r="P670" s="26"/>
     </row>
     <row r="671" spans="2:16">
-      <c r="B671" s="49">
+      <c r="B671" s="47">
         <v>46091</v>
       </c>
       <c r="C671" s="32" t="s">
@@ -21663,7 +21691,7 @@
       <c r="P671" s="26"/>
     </row>
     <row r="672" spans="2:16">
-      <c r="B672" s="49">
+      <c r="B672" s="47">
         <v>46091</v>
       </c>
       <c r="C672" s="32" t="s">
@@ -21692,7 +21720,7 @@
       <c r="P672" s="26"/>
     </row>
     <row r="673" spans="2:16">
-      <c r="B673" s="49">
+      <c r="B673" s="47">
         <v>46091</v>
       </c>
       <c r="C673" s="32" t="s">
@@ -21721,7 +21749,7 @@
       <c r="P673" s="26"/>
     </row>
     <row r="674" spans="2:16">
-      <c r="B674" s="49">
+      <c r="B674" s="47">
         <v>46091</v>
       </c>
       <c r="C674" s="32" t="s">
@@ -21752,7 +21780,7 @@
       <c r="P674" s="26"/>
     </row>
     <row r="675" spans="2:16">
-      <c r="B675" s="49">
+      <c r="B675" s="47">
         <v>46091</v>
       </c>
       <c r="C675" s="32" t="s">
@@ -21781,7 +21809,7 @@
       <c r="P675" s="26"/>
     </row>
     <row r="676" spans="2:16">
-      <c r="B676" s="49">
+      <c r="B676" s="47">
         <v>46091</v>
       </c>
       <c r="C676" s="32" t="s">
@@ -21810,7 +21838,7 @@
       <c r="P676" s="26"/>
     </row>
     <row r="677" spans="2:16">
-      <c r="B677" s="49">
+      <c r="B677" s="47">
         <v>46091</v>
       </c>
       <c r="C677" s="32" t="s">
@@ -21839,7 +21867,7 @@
       <c r="P677" s="26"/>
     </row>
     <row r="678" spans="2:16">
-      <c r="B678" s="49">
+      <c r="B678" s="47">
         <v>46091</v>
       </c>
       <c r="C678" s="32" t="s">
@@ -21868,7 +21896,7 @@
       <c r="P678" s="26"/>
     </row>
     <row r="679" spans="2:16">
-      <c r="B679" s="49">
+      <c r="B679" s="47">
         <v>46091</v>
       </c>
       <c r="C679" s="32" t="s">
@@ -21897,7 +21925,7 @@
       <c r="P679" s="26"/>
     </row>
     <row r="680" spans="2:16">
-      <c r="B680" s="49">
+      <c r="B680" s="47">
         <v>46091</v>
       </c>
       <c r="C680" s="37" t="s">
@@ -21928,7 +21956,7 @@
       <c r="P680" s="26"/>
     </row>
     <row r="681" spans="2:16">
-      <c r="B681" s="49">
+      <c r="B681" s="47">
         <v>46091</v>
       </c>
       <c r="C681" s="37" t="s">
@@ -21959,7 +21987,7 @@
       </c>
     </row>
     <row r="682" spans="2:16">
-      <c r="B682" s="49">
+      <c r="B682" s="47">
         <v>46091</v>
       </c>
       <c r="C682" s="37" t="s">
@@ -21994,7 +22022,7 @@
       </c>
     </row>
     <row r="683" spans="2:16">
-      <c r="B683" s="49">
+      <c r="B683" s="47">
         <v>46091</v>
       </c>
       <c r="C683" s="37" t="s">
@@ -22021,6 +22049,1489 @@
       <c r="N683" s="26"/>
       <c r="O683" s="26"/>
       <c r="P683" s="26"/>
+    </row>
+    <row r="684" spans="2:16">
+      <c r="B684" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C684" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="D684" s="26">
+        <v>70</v>
+      </c>
+      <c r="E684" s="43">
+        <f t="shared" si="20"/>
+        <v>70</v>
+      </c>
+      <c r="F684" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G684" s="26"/>
+      <c r="H684" s="26"/>
+      <c r="I684" s="33"/>
+      <c r="J684" s="33"/>
+      <c r="K684" s="33"/>
+      <c r="L684" s="26"/>
+      <c r="M684" s="26"/>
+      <c r="N684" s="26"/>
+      <c r="O684" s="26"/>
+      <c r="P684" s="33"/>
+    </row>
+    <row r="685" spans="2:16">
+      <c r="B685" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C685" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="D685" s="26">
+        <v>149</v>
+      </c>
+      <c r="E685" s="43">
+        <f t="shared" si="20"/>
+        <v>140</v>
+      </c>
+      <c r="F685" s="8">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="G685" s="26"/>
+      <c r="H685" s="26">
+        <v>9</v>
+      </c>
+      <c r="I685" s="26"/>
+      <c r="J685" s="26"/>
+      <c r="K685" s="26"/>
+      <c r="L685" s="26"/>
+      <c r="M685" s="26"/>
+      <c r="N685" s="26"/>
+      <c r="O685" s="26"/>
+      <c r="P685" s="26"/>
+    </row>
+    <row r="686" spans="2:16">
+      <c r="B686" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C686" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="D686" s="26">
+        <v>83</v>
+      </c>
+      <c r="E686" s="43">
+        <f t="shared" si="20"/>
+        <v>70</v>
+      </c>
+      <c r="F686" s="8">
+        <f t="shared" si="21"/>
+        <v>13</v>
+      </c>
+      <c r="G686" s="26">
+        <v>13</v>
+      </c>
+      <c r="H686" s="26"/>
+      <c r="I686" s="26"/>
+      <c r="J686" s="26"/>
+      <c r="K686" s="26"/>
+      <c r="L686" s="26"/>
+      <c r="M686" s="26"/>
+      <c r="N686" s="26"/>
+      <c r="O686" s="26"/>
+      <c r="P686" s="26"/>
+    </row>
+    <row r="687" spans="2:16">
+      <c r="B687" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C687" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="D687" s="26">
+        <v>154</v>
+      </c>
+      <c r="E687" s="43">
+        <f t="shared" si="20"/>
+        <v>150</v>
+      </c>
+      <c r="F687" s="8">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="G687" s="26">
+        <v>4</v>
+      </c>
+      <c r="H687" s="26"/>
+      <c r="I687" s="26"/>
+      <c r="J687" s="26"/>
+      <c r="K687" s="26"/>
+      <c r="L687" s="26"/>
+      <c r="M687" s="26"/>
+      <c r="N687" s="26"/>
+      <c r="O687" s="26"/>
+      <c r="P687" s="26"/>
+    </row>
+    <row r="688" spans="2:16">
+      <c r="B688" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C688" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="D688" s="26">
+        <v>387</v>
+      </c>
+      <c r="E688" s="43">
+        <f t="shared" si="20"/>
+        <v>380</v>
+      </c>
+      <c r="F688" s="8">
+        <f t="shared" si="21"/>
+        <v>7</v>
+      </c>
+      <c r="G688" s="26"/>
+      <c r="H688" s="26">
+        <v>7</v>
+      </c>
+      <c r="I688" s="26"/>
+      <c r="J688" s="26"/>
+      <c r="K688" s="26"/>
+      <c r="L688" s="26"/>
+      <c r="M688" s="26"/>
+      <c r="N688" s="26"/>
+      <c r="O688" s="26"/>
+      <c r="P688" s="26"/>
+    </row>
+    <row r="689" spans="2:16">
+      <c r="B689" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C689" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="D689" s="26">
+        <v>204</v>
+      </c>
+      <c r="E689" s="43">
+        <f t="shared" si="20"/>
+        <v>200</v>
+      </c>
+      <c r="F689" s="8">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="G689" s="26">
+        <v>4</v>
+      </c>
+      <c r="H689" s="26"/>
+      <c r="I689" s="26"/>
+      <c r="J689" s="26"/>
+      <c r="K689" s="26"/>
+      <c r="L689" s="26"/>
+      <c r="M689" s="26"/>
+      <c r="N689" s="26"/>
+      <c r="O689" s="26"/>
+      <c r="P689" s="26"/>
+    </row>
+    <row r="690" spans="2:16">
+      <c r="B690" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C690" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="D690" s="26">
+        <v>104</v>
+      </c>
+      <c r="E690" s="43">
+        <f t="shared" si="20"/>
+        <v>100</v>
+      </c>
+      <c r="F690" s="8">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="G690" s="26">
+        <v>4</v>
+      </c>
+      <c r="H690" s="26"/>
+      <c r="I690" s="26"/>
+      <c r="J690" s="26"/>
+      <c r="K690" s="26"/>
+      <c r="L690" s="26"/>
+      <c r="M690" s="26"/>
+      <c r="N690" s="26"/>
+      <c r="O690" s="26"/>
+      <c r="P690" s="26"/>
+    </row>
+    <row r="691" spans="2:16">
+      <c r="B691" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C691" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="D691" s="26">
+        <v>219</v>
+      </c>
+      <c r="E691" s="43">
+        <f t="shared" si="20"/>
+        <v>210</v>
+      </c>
+      <c r="F691" s="8">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="G691" s="26"/>
+      <c r="H691" s="26">
+        <v>9</v>
+      </c>
+      <c r="I691" s="26"/>
+      <c r="J691" s="26"/>
+      <c r="K691" s="26"/>
+      <c r="L691" s="26"/>
+      <c r="M691" s="26"/>
+      <c r="N691" s="26"/>
+      <c r="O691" s="26"/>
+      <c r="P691" s="26"/>
+    </row>
+    <row r="692" spans="2:16">
+      <c r="B692" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C692" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="D692" s="26">
+        <v>270</v>
+      </c>
+      <c r="E692" s="43">
+        <f t="shared" si="20"/>
+        <v>252</v>
+      </c>
+      <c r="F692" s="8">
+        <f t="shared" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="G692" s="26"/>
+      <c r="H692" s="26">
+        <v>18</v>
+      </c>
+      <c r="I692" s="26"/>
+      <c r="J692" s="26"/>
+      <c r="K692" s="26"/>
+      <c r="L692" s="26"/>
+      <c r="M692" s="26"/>
+      <c r="N692" s="26"/>
+      <c r="O692" s="26"/>
+      <c r="P692" s="26"/>
+    </row>
+    <row r="693" spans="2:16">
+      <c r="B693" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C693" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D693" s="26">
+        <v>1809</v>
+      </c>
+      <c r="E693" s="43">
+        <f t="shared" si="20"/>
+        <v>1800</v>
+      </c>
+      <c r="F693" s="8">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="G693" s="26"/>
+      <c r="H693" s="26">
+        <v>9</v>
+      </c>
+      <c r="I693" s="26"/>
+      <c r="J693" s="26"/>
+      <c r="K693" s="34"/>
+      <c r="L693" s="26"/>
+      <c r="M693" s="26"/>
+      <c r="N693" s="26"/>
+      <c r="O693" s="26"/>
+      <c r="P693" s="26"/>
+    </row>
+    <row r="694" spans="2:16">
+      <c r="B694" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C694" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D694" s="26">
+        <v>1700</v>
+      </c>
+      <c r="E694" s="43">
+        <f t="shared" si="20"/>
+        <v>1700</v>
+      </c>
+      <c r="F694" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G694" s="26"/>
+      <c r="H694" s="26"/>
+      <c r="I694" s="26"/>
+      <c r="J694" s="26"/>
+      <c r="K694" s="26"/>
+      <c r="L694" s="26"/>
+      <c r="M694" s="26"/>
+      <c r="N694" s="26"/>
+      <c r="O694" s="26"/>
+      <c r="P694" s="26"/>
+    </row>
+    <row r="695" spans="2:16">
+      <c r="B695" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C695" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D695" s="26">
+        <v>20</v>
+      </c>
+      <c r="E695" s="43">
+        <f t="shared" si="20"/>
+        <v>20</v>
+      </c>
+      <c r="F695" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G695" s="26"/>
+      <c r="H695" s="26"/>
+      <c r="I695" s="26"/>
+      <c r="J695" s="26"/>
+      <c r="K695" s="26"/>
+      <c r="L695" s="26"/>
+      <c r="M695" s="26"/>
+      <c r="N695" s="26"/>
+      <c r="O695" s="26"/>
+      <c r="P695" s="26"/>
+    </row>
+    <row r="696" spans="2:16">
+      <c r="B696" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C696" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D696" s="26">
+        <v>664</v>
+      </c>
+      <c r="E696" s="43">
+        <f t="shared" si="20"/>
+        <v>660</v>
+      </c>
+      <c r="F696" s="8">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="G696" s="26"/>
+      <c r="H696" s="26">
+        <v>4</v>
+      </c>
+      <c r="I696" s="26"/>
+      <c r="J696" s="26"/>
+      <c r="K696" s="26"/>
+      <c r="L696" s="26"/>
+      <c r="M696" s="26"/>
+      <c r="N696" s="26"/>
+      <c r="O696" s="26"/>
+      <c r="P696" s="26"/>
+    </row>
+    <row r="697" spans="2:16">
+      <c r="B697" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C697" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D697" s="26">
+        <v>1127</v>
+      </c>
+      <c r="E697" s="43">
+        <f t="shared" si="20"/>
+        <v>1120</v>
+      </c>
+      <c r="F697" s="8">
+        <f t="shared" si="21"/>
+        <v>7</v>
+      </c>
+      <c r="G697" s="26"/>
+      <c r="H697" s="26">
+        <v>7</v>
+      </c>
+      <c r="I697" s="26"/>
+      <c r="J697" s="26"/>
+      <c r="K697" s="26"/>
+      <c r="L697" s="26"/>
+      <c r="M697" s="26"/>
+      <c r="N697" s="26"/>
+      <c r="O697" s="26"/>
+      <c r="P697" s="26"/>
+    </row>
+    <row r="698" spans="2:16">
+      <c r="B698" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C698" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D698" s="26">
+        <v>1710</v>
+      </c>
+      <c r="E698" s="43">
+        <f t="shared" si="20"/>
+        <v>1710</v>
+      </c>
+      <c r="F698" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G698" s="26"/>
+      <c r="H698" s="26"/>
+      <c r="I698" s="26"/>
+      <c r="J698" s="26"/>
+      <c r="K698" s="26"/>
+      <c r="L698" s="26"/>
+      <c r="M698" s="26"/>
+      <c r="N698" s="26"/>
+      <c r="O698" s="26"/>
+      <c r="P698" s="26"/>
+    </row>
+    <row r="699" spans="2:16">
+      <c r="B699" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C699" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="D699" s="26">
+        <v>50</v>
+      </c>
+      <c r="E699" s="43">
+        <f t="shared" si="20"/>
+        <v>50</v>
+      </c>
+      <c r="F699" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G699" s="26"/>
+      <c r="H699" s="26"/>
+      <c r="I699" s="26"/>
+      <c r="J699" s="26"/>
+      <c r="K699" s="26"/>
+      <c r="L699" s="26"/>
+      <c r="M699" s="26"/>
+      <c r="N699" s="26"/>
+      <c r="O699" s="26"/>
+      <c r="P699" s="26"/>
+    </row>
+    <row r="700" spans="2:16">
+      <c r="B700" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C700" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="D700" s="26">
+        <v>912</v>
+      </c>
+      <c r="E700" s="43">
+        <f t="shared" si="20"/>
+        <v>912</v>
+      </c>
+      <c r="F700" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G700" s="26"/>
+      <c r="H700" s="26"/>
+      <c r="I700" s="26"/>
+      <c r="J700" s="26"/>
+      <c r="K700" s="26"/>
+      <c r="L700" s="26"/>
+      <c r="M700" s="26"/>
+      <c r="N700" s="26"/>
+      <c r="O700" s="26"/>
+      <c r="P700" s="26"/>
+    </row>
+    <row r="701" spans="2:16">
+      <c r="B701" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C701" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D701" s="26">
+        <v>93</v>
+      </c>
+      <c r="E701" s="43">
+        <f t="shared" si="20"/>
+        <v>90</v>
+      </c>
+      <c r="F701" s="8">
+        <f t="shared" si="21"/>
+        <v>3</v>
+      </c>
+      <c r="G701" s="26"/>
+      <c r="H701" s="26">
+        <v>3</v>
+      </c>
+      <c r="I701" s="26"/>
+      <c r="J701" s="26"/>
+      <c r="K701" s="26"/>
+      <c r="L701" s="26"/>
+      <c r="M701" s="26"/>
+      <c r="N701" s="26"/>
+      <c r="O701" s="26"/>
+      <c r="P701" s="26"/>
+    </row>
+    <row r="702" spans="2:16">
+      <c r="B702" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C702" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="D702" s="26">
+        <v>720</v>
+      </c>
+      <c r="E702" s="43">
+        <f t="shared" si="20"/>
+        <v>720</v>
+      </c>
+      <c r="F702" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G702" s="26"/>
+      <c r="H702" s="26"/>
+      <c r="I702" s="26"/>
+      <c r="J702" s="26"/>
+      <c r="K702" s="26"/>
+      <c r="L702" s="26"/>
+      <c r="M702" s="26"/>
+      <c r="N702" s="26"/>
+      <c r="O702" s="26"/>
+      <c r="P702" s="26"/>
+    </row>
+    <row r="703" spans="2:16">
+      <c r="B703" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C703" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="D703" s="26">
+        <v>1100</v>
+      </c>
+      <c r="E703" s="43">
+        <f t="shared" si="20"/>
+        <v>1100</v>
+      </c>
+      <c r="F703" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G703" s="26"/>
+      <c r="H703" s="26"/>
+      <c r="I703" s="26"/>
+      <c r="J703" s="26"/>
+      <c r="K703" s="26"/>
+      <c r="L703" s="26"/>
+      <c r="M703" s="26"/>
+      <c r="N703" s="26"/>
+      <c r="O703" s="26"/>
+      <c r="P703" s="26"/>
+    </row>
+    <row r="704" spans="2:16">
+      <c r="B704" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C704" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="D704" s="26">
+        <v>78</v>
+      </c>
+      <c r="E704" s="43">
+        <f t="shared" si="20"/>
+        <v>78</v>
+      </c>
+      <c r="F704" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G704" s="26"/>
+      <c r="H704" s="26"/>
+      <c r="I704" s="26"/>
+      <c r="J704" s="26"/>
+      <c r="K704" s="26"/>
+      <c r="L704" s="26"/>
+      <c r="M704" s="26"/>
+      <c r="N704" s="26"/>
+      <c r="O704" s="26"/>
+      <c r="P704" s="26"/>
+    </row>
+    <row r="705" spans="2:16">
+      <c r="B705" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C705" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D705" s="26">
+        <v>233</v>
+      </c>
+      <c r="E705" s="43">
+        <f t="shared" si="20"/>
+        <v>230</v>
+      </c>
+      <c r="F705" s="8">
+        <f t="shared" si="21"/>
+        <v>3</v>
+      </c>
+      <c r="G705" s="26"/>
+      <c r="H705" s="26"/>
+      <c r="I705" s="26"/>
+      <c r="J705" s="26"/>
+      <c r="K705" s="26"/>
+      <c r="L705" s="26"/>
+      <c r="M705" s="26"/>
+      <c r="N705" s="26"/>
+      <c r="O705" s="26"/>
+      <c r="P705" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="706" spans="2:16">
+      <c r="B706" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C706" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D706" s="26">
+        <v>30</v>
+      </c>
+      <c r="E706" s="43">
+        <f t="shared" si="20"/>
+        <v>30</v>
+      </c>
+      <c r="F706" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G706" s="26"/>
+      <c r="H706" s="26"/>
+      <c r="I706" s="26"/>
+      <c r="J706" s="26"/>
+      <c r="K706" s="26"/>
+      <c r="L706" s="26"/>
+      <c r="M706" s="26"/>
+      <c r="N706" s="26"/>
+      <c r="O706" s="26"/>
+      <c r="P706" s="26"/>
+    </row>
+    <row r="707" spans="2:16">
+      <c r="B707" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C707" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="D707" s="26">
+        <v>732</v>
+      </c>
+      <c r="E707" s="43">
+        <f t="shared" si="20"/>
+        <v>718</v>
+      </c>
+      <c r="F707" s="8">
+        <f t="shared" si="21"/>
+        <v>14</v>
+      </c>
+      <c r="G707" s="26">
+        <v>9</v>
+      </c>
+      <c r="H707" s="26">
+        <v>5</v>
+      </c>
+      <c r="I707" s="26"/>
+      <c r="J707" s="26"/>
+      <c r="K707" s="26"/>
+      <c r="L707" s="26"/>
+      <c r="M707" s="26"/>
+      <c r="N707" s="26"/>
+      <c r="O707" s="26"/>
+      <c r="P707" s="26"/>
+    </row>
+    <row r="708" spans="2:16">
+      <c r="B708" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C708" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="D708" s="26">
+        <v>517</v>
+      </c>
+      <c r="E708" s="43">
+        <f t="shared" si="20"/>
+        <v>515</v>
+      </c>
+      <c r="F708" s="8">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+      <c r="G708" s="26"/>
+      <c r="H708" s="26">
+        <v>2</v>
+      </c>
+      <c r="I708" s="26"/>
+      <c r="J708" s="26"/>
+      <c r="K708" s="26"/>
+      <c r="L708" s="26"/>
+      <c r="M708" s="26"/>
+      <c r="N708" s="26"/>
+      <c r="O708" s="26"/>
+      <c r="P708" s="26"/>
+    </row>
+    <row r="709" spans="2:16">
+      <c r="B709" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C709" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="D709" s="26">
+        <v>459</v>
+      </c>
+      <c r="E709" s="43">
+        <f t="shared" si="20"/>
+        <v>459</v>
+      </c>
+      <c r="F709" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G709" s="26"/>
+      <c r="H709" s="26"/>
+      <c r="I709" s="26"/>
+      <c r="J709" s="26"/>
+      <c r="K709" s="26"/>
+      <c r="L709" s="26"/>
+      <c r="M709" s="26"/>
+      <c r="N709" s="26"/>
+      <c r="O709" s="26"/>
+      <c r="P709" s="26"/>
+    </row>
+    <row r="710" spans="2:16">
+      <c r="B710" s="47">
+        <v>46092</v>
+      </c>
+      <c r="C710" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="D710" s="26">
+        <v>104</v>
+      </c>
+      <c r="E710" s="43">
+        <f t="shared" si="20"/>
+        <v>100</v>
+      </c>
+      <c r="F710" s="8">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="G710" s="26"/>
+      <c r="H710" s="26">
+        <v>4</v>
+      </c>
+      <c r="I710" s="26"/>
+      <c r="J710" s="26"/>
+      <c r="K710" s="26"/>
+      <c r="L710" s="26"/>
+      <c r="M710" s="26"/>
+      <c r="N710" s="26"/>
+      <c r="O710" s="26"/>
+      <c r="P710" s="26"/>
+    </row>
+    <row r="711" spans="2:16">
+      <c r="B711" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C711" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="D711" s="26">
+        <v>470</v>
+      </c>
+      <c r="E711" s="43">
+        <f t="shared" si="20"/>
+        <v>470</v>
+      </c>
+      <c r="F711" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G711" s="26"/>
+      <c r="H711" s="26"/>
+      <c r="I711" s="33"/>
+      <c r="J711" s="33"/>
+      <c r="K711" s="33"/>
+      <c r="L711" s="26"/>
+      <c r="M711" s="26"/>
+      <c r="N711" s="26"/>
+      <c r="O711" s="26"/>
+      <c r="P711" s="33"/>
+    </row>
+    <row r="712" spans="2:16">
+      <c r="B712" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C712" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="D712" s="26">
+        <v>420</v>
+      </c>
+      <c r="E712" s="43">
+        <f t="shared" si="20"/>
+        <v>420</v>
+      </c>
+      <c r="F712" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G712" s="26"/>
+      <c r="H712" s="26"/>
+      <c r="I712" s="26"/>
+      <c r="J712" s="26"/>
+      <c r="K712" s="26"/>
+      <c r="L712" s="26"/>
+      <c r="M712" s="26"/>
+      <c r="N712" s="26"/>
+      <c r="O712" s="26"/>
+      <c r="P712" s="26"/>
+    </row>
+    <row r="713" spans="2:16">
+      <c r="B713" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C713" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D713" s="26">
+        <v>100</v>
+      </c>
+      <c r="E713" s="43">
+        <f t="shared" si="20"/>
+        <v>100</v>
+      </c>
+      <c r="F713" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G713" s="26"/>
+      <c r="H713" s="26"/>
+      <c r="I713" s="26"/>
+      <c r="J713" s="26"/>
+      <c r="K713" s="26"/>
+      <c r="L713" s="26"/>
+      <c r="M713" s="26"/>
+      <c r="N713" s="26"/>
+      <c r="O713" s="26"/>
+      <c r="P713" s="26"/>
+    </row>
+    <row r="714" spans="2:16">
+      <c r="B714" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C714" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="D714" s="26">
+        <v>242</v>
+      </c>
+      <c r="E714" s="43">
+        <f t="shared" si="20"/>
+        <v>240</v>
+      </c>
+      <c r="F714" s="8">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+      <c r="G714" s="26"/>
+      <c r="H714" s="26">
+        <v>2</v>
+      </c>
+      <c r="I714" s="26"/>
+      <c r="J714" s="26"/>
+      <c r="K714" s="26"/>
+      <c r="L714" s="26"/>
+      <c r="M714" s="26"/>
+      <c r="N714" s="26"/>
+      <c r="O714" s="26"/>
+      <c r="P714" s="26"/>
+    </row>
+    <row r="715" spans="2:16">
+      <c r="B715" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C715" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D715" s="26">
+        <v>463</v>
+      </c>
+      <c r="E715" s="43">
+        <f t="shared" si="20"/>
+        <v>450</v>
+      </c>
+      <c r="F715" s="8">
+        <f t="shared" si="21"/>
+        <v>13</v>
+      </c>
+      <c r="G715" s="26">
+        <v>8</v>
+      </c>
+      <c r="H715" s="26">
+        <v>5</v>
+      </c>
+      <c r="I715" s="26"/>
+      <c r="J715" s="26"/>
+      <c r="K715" s="26"/>
+      <c r="L715" s="26"/>
+      <c r="M715" s="26"/>
+      <c r="N715" s="26"/>
+      <c r="O715" s="26"/>
+      <c r="P715" s="26"/>
+    </row>
+    <row r="716" spans="2:16">
+      <c r="B716" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C716" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="D716" s="26">
+        <v>192</v>
+      </c>
+      <c r="E716" s="43">
+        <f t="shared" si="20"/>
+        <v>192</v>
+      </c>
+      <c r="F716" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G716" s="26"/>
+      <c r="H716" s="26"/>
+      <c r="I716" s="26"/>
+      <c r="J716" s="26"/>
+      <c r="K716" s="26"/>
+      <c r="L716" s="26"/>
+      <c r="M716" s="26"/>
+      <c r="N716" s="26"/>
+      <c r="O716" s="26"/>
+      <c r="P716" s="26"/>
+    </row>
+    <row r="717" spans="2:16">
+      <c r="B717" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C717" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D717" s="26">
+        <v>65</v>
+      </c>
+      <c r="E717" s="43">
+        <f t="shared" si="20"/>
+        <v>58</v>
+      </c>
+      <c r="F717" s="8">
+        <f t="shared" si="21"/>
+        <v>7</v>
+      </c>
+      <c r="G717" s="26"/>
+      <c r="H717" s="26">
+        <v>7</v>
+      </c>
+      <c r="I717" s="26"/>
+      <c r="J717" s="26"/>
+      <c r="K717" s="26"/>
+      <c r="L717" s="26"/>
+      <c r="M717" s="26"/>
+      <c r="N717" s="26"/>
+      <c r="O717" s="26"/>
+      <c r="P717" s="26"/>
+    </row>
+    <row r="718" spans="2:16">
+      <c r="B718" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C718" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D718" s="26">
+        <v>1798</v>
+      </c>
+      <c r="E718" s="43">
+        <f t="shared" si="20"/>
+        <v>1780</v>
+      </c>
+      <c r="F718" s="8">
+        <f t="shared" si="21"/>
+        <v>18</v>
+      </c>
+      <c r="G718" s="26"/>
+      <c r="H718" s="26"/>
+      <c r="I718" s="26"/>
+      <c r="J718" s="26"/>
+      <c r="K718" s="26"/>
+      <c r="L718" s="26">
+        <v>18</v>
+      </c>
+      <c r="M718" s="26"/>
+      <c r="N718" s="26"/>
+      <c r="O718" s="26"/>
+      <c r="P718" s="26"/>
+    </row>
+    <row r="719" spans="2:16">
+      <c r="B719" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C719" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="D719" s="26">
+        <v>1654</v>
+      </c>
+      <c r="E719" s="43">
+        <f t="shared" si="20"/>
+        <v>1650</v>
+      </c>
+      <c r="F719" s="8">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="G719" s="26"/>
+      <c r="H719" s="26">
+        <v>4</v>
+      </c>
+      <c r="I719" s="26"/>
+      <c r="J719" s="26"/>
+      <c r="K719" s="26"/>
+      <c r="L719" s="26"/>
+      <c r="M719" s="26"/>
+      <c r="N719" s="26"/>
+      <c r="O719" s="26"/>
+      <c r="P719" s="26"/>
+    </row>
+    <row r="720" spans="2:16">
+      <c r="B720" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C720" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D720" s="26">
+        <v>722</v>
+      </c>
+      <c r="E720" s="43">
+        <f t="shared" si="20"/>
+        <v>720</v>
+      </c>
+      <c r="F720" s="8">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+      <c r="G720" s="26"/>
+      <c r="H720" s="26">
+        <v>2</v>
+      </c>
+      <c r="I720" s="26"/>
+      <c r="J720" s="26"/>
+      <c r="K720" s="26"/>
+      <c r="L720" s="26"/>
+      <c r="M720" s="26"/>
+      <c r="N720" s="26"/>
+      <c r="O720" s="26"/>
+      <c r="P720" s="26"/>
+    </row>
+    <row r="721" spans="2:16">
+      <c r="B721" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C721" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="D721" s="26">
+        <v>459</v>
+      </c>
+      <c r="E721" s="43">
+        <f t="shared" ref="E721:E732" si="22">D721-F721</f>
+        <v>452</v>
+      </c>
+      <c r="F721" s="8">
+        <f t="shared" si="21"/>
+        <v>7</v>
+      </c>
+      <c r="G721" s="26"/>
+      <c r="H721" s="26"/>
+      <c r="I721" s="26"/>
+      <c r="J721" s="26">
+        <v>7</v>
+      </c>
+      <c r="K721" s="26"/>
+      <c r="L721" s="26"/>
+      <c r="M721" s="26"/>
+      <c r="N721" s="26"/>
+      <c r="O721" s="26"/>
+      <c r="P721" s="26"/>
+    </row>
+    <row r="722" spans="2:16">
+      <c r="B722" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C722" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="D722" s="26">
+        <v>256</v>
+      </c>
+      <c r="E722" s="43">
+        <f t="shared" si="22"/>
+        <v>256</v>
+      </c>
+      <c r="F722" s="8">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="G722" s="26"/>
+      <c r="H722" s="26"/>
+      <c r="I722" s="26"/>
+      <c r="J722" s="26"/>
+      <c r="K722" s="26"/>
+      <c r="L722" s="26"/>
+      <c r="M722" s="26"/>
+      <c r="N722" s="26"/>
+      <c r="O722" s="26"/>
+      <c r="P722" s="26"/>
+    </row>
+    <row r="723" spans="2:16">
+      <c r="B723" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C723" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="D723" s="26">
+        <v>544</v>
+      </c>
+      <c r="E723" s="43">
+        <f t="shared" si="22"/>
+        <v>540</v>
+      </c>
+      <c r="F723" s="8">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="G723" s="26">
+        <v>4</v>
+      </c>
+      <c r="H723" s="26"/>
+      <c r="I723" s="26"/>
+      <c r="J723" s="26"/>
+      <c r="K723" s="26"/>
+      <c r="L723" s="26"/>
+      <c r="M723" s="26"/>
+      <c r="N723" s="26"/>
+      <c r="O723" s="26"/>
+      <c r="P723" s="26"/>
+    </row>
+    <row r="724" spans="2:16">
+      <c r="B724" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C724" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D724" s="26">
+        <v>426</v>
+      </c>
+      <c r="E724" s="43">
+        <f t="shared" si="22"/>
+        <v>420</v>
+      </c>
+      <c r="F724" s="8">
+        <f t="shared" ref="F724:F732" si="23">SUM(G724:P724)</f>
+        <v>6</v>
+      </c>
+      <c r="G724" s="26"/>
+      <c r="H724" s="26">
+        <v>5</v>
+      </c>
+      <c r="I724" s="26"/>
+      <c r="J724" s="26"/>
+      <c r="K724" s="26"/>
+      <c r="L724" s="26"/>
+      <c r="M724" s="26"/>
+      <c r="N724" s="26"/>
+      <c r="O724" s="26"/>
+      <c r="P724" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725" spans="2:16">
+      <c r="B725" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C725" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="D725" s="26">
+        <v>70</v>
+      </c>
+      <c r="E725" s="43">
+        <f t="shared" si="22"/>
+        <v>70</v>
+      </c>
+      <c r="F725" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="G725" s="26"/>
+      <c r="H725" s="26"/>
+      <c r="I725" s="26"/>
+      <c r="J725" s="26"/>
+      <c r="K725" s="26"/>
+      <c r="L725" s="26"/>
+      <c r="M725" s="26"/>
+      <c r="N725" s="26"/>
+      <c r="O725" s="26"/>
+      <c r="P725" s="26"/>
+    </row>
+    <row r="726" spans="2:16">
+      <c r="B726" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C726" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="D726" s="26">
+        <v>609</v>
+      </c>
+      <c r="E726" s="43">
+        <f t="shared" si="22"/>
+        <v>600</v>
+      </c>
+      <c r="F726" s="8">
+        <f t="shared" si="23"/>
+        <v>9</v>
+      </c>
+      <c r="G726" s="26"/>
+      <c r="H726" s="26"/>
+      <c r="I726" s="26"/>
+      <c r="J726" s="26"/>
+      <c r="K726" s="26"/>
+      <c r="L726" s="26"/>
+      <c r="M726" s="26"/>
+      <c r="N726" s="26"/>
+      <c r="O726" s="26"/>
+      <c r="P726" s="26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="727" spans="2:16">
+      <c r="B727" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C727" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D727" s="26">
+        <v>1600</v>
+      </c>
+      <c r="E727" s="43">
+        <f t="shared" si="22"/>
+        <v>1600</v>
+      </c>
+      <c r="F727" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="G727" s="26"/>
+      <c r="H727" s="26"/>
+      <c r="I727" s="26"/>
+      <c r="J727" s="26"/>
+      <c r="K727" s="26"/>
+      <c r="L727" s="26"/>
+      <c r="M727" s="26"/>
+      <c r="N727" s="26"/>
+      <c r="O727" s="26"/>
+      <c r="P727" s="26"/>
+    </row>
+    <row r="728" spans="2:16">
+      <c r="B728" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C728" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="D728" s="26">
+        <v>20</v>
+      </c>
+      <c r="E728" s="43">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="F728" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="G728" s="26"/>
+      <c r="H728" s="26"/>
+      <c r="I728" s="26"/>
+      <c r="J728" s="26"/>
+      <c r="K728" s="26"/>
+      <c r="L728" s="26"/>
+      <c r="M728" s="26"/>
+      <c r="N728" s="26"/>
+      <c r="O728" s="26"/>
+      <c r="P728" s="26"/>
+    </row>
+    <row r="729" spans="2:16">
+      <c r="B729" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C729" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D729" s="26">
+        <v>170</v>
+      </c>
+      <c r="E729" s="43">
+        <f t="shared" si="22"/>
+        <v>170</v>
+      </c>
+      <c r="F729" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="G729" s="26"/>
+      <c r="H729" s="26"/>
+      <c r="I729" s="26"/>
+      <c r="J729" s="26"/>
+      <c r="K729" s="26"/>
+      <c r="L729" s="26"/>
+      <c r="M729" s="26"/>
+      <c r="N729" s="26"/>
+      <c r="O729" s="26"/>
+      <c r="P729" s="26"/>
+    </row>
+    <row r="730" spans="2:16">
+      <c r="B730" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C730" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="D730" s="26">
+        <v>20</v>
+      </c>
+      <c r="E730" s="43">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="F730" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="G730" s="26"/>
+      <c r="H730" s="26"/>
+      <c r="I730" s="26"/>
+      <c r="J730" s="26"/>
+      <c r="K730" s="26"/>
+      <c r="L730" s="26"/>
+      <c r="M730" s="26"/>
+      <c r="N730" s="26"/>
+      <c r="O730" s="26"/>
+      <c r="P730" s="26"/>
+    </row>
+    <row r="731" spans="2:16">
+      <c r="B731" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C731" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="D731" s="26">
+        <v>1302</v>
+      </c>
+      <c r="E731" s="43">
+        <f t="shared" si="22"/>
+        <v>1300</v>
+      </c>
+      <c r="F731" s="8">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="G731" s="26"/>
+      <c r="H731" s="26">
+        <v>2</v>
+      </c>
+      <c r="I731" s="26"/>
+      <c r="J731" s="26"/>
+      <c r="K731" s="26"/>
+      <c r="L731" s="26"/>
+      <c r="M731" s="26"/>
+      <c r="N731" s="26"/>
+      <c r="O731" s="26"/>
+      <c r="P731" s="26"/>
+    </row>
+    <row r="732" spans="2:16">
+      <c r="B732" s="47">
+        <v>46093</v>
+      </c>
+      <c r="C732" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="D732" s="26">
+        <v>1544</v>
+      </c>
+      <c r="E732" s="43">
+        <f t="shared" si="22"/>
+        <v>1540</v>
+      </c>
+      <c r="F732" s="8">
+        <f t="shared" si="23"/>
+        <v>4</v>
+      </c>
+      <c r="G732" s="26"/>
+      <c r="H732" s="26">
+        <v>4</v>
+      </c>
+      <c r="I732" s="26"/>
+      <c r="J732" s="26"/>
+      <c r="K732" s="26"/>
+      <c r="L732" s="26"/>
+      <c r="M732" s="26"/>
+      <c r="N732" s="26"/>
+      <c r="O732" s="26"/>
+      <c r="P732" s="26"/>
     </row>
     <row r="63289" spans="2:2">
       <c r="B63289" s="15"/>
